--- a/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251459751315618</v>
+        <v>1.250301289024606</v>
       </c>
       <c r="C3" t="n">
-        <v>4.657614221781809</v>
+        <v>4.638882475584779</v>
       </c>
       <c r="D3" t="n">
-        <v>6.155690735502215</v>
+        <v>6.181707049664754</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06476470859964</v>
+        <v>12.07089081427414</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370457293817605</v>
+        <v>1.362317557640158</v>
       </c>
       <c r="C4" t="n">
-        <v>5.20957454423788</v>
+        <v>5.164271220097906</v>
       </c>
       <c r="D4" t="n">
-        <v>6.49002353288924</v>
+        <v>6.497396334888224</v>
       </c>
       <c r="E4" t="n">
-        <v>13.07005537094473</v>
+        <v>13.02398511262629</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.535290288829396</v>
+        <v>1.513473540924739</v>
       </c>
       <c r="C5" t="n">
-        <v>5.965347988691463</v>
+        <v>5.83817498314566</v>
       </c>
       <c r="D5" t="n">
-        <v>6.834485492132768</v>
+        <v>6.867463977215419</v>
       </c>
       <c r="E5" t="n">
-        <v>14.33512376965363</v>
+        <v>14.21911250128582</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.724799858754502</v>
+        <v>1.689271657366392</v>
       </c>
       <c r="C6" t="n">
-        <v>6.912390285554457</v>
+        <v>6.682171189649</v>
       </c>
       <c r="D6" t="n">
-        <v>7.19525020614682</v>
+        <v>7.237846096671976</v>
       </c>
       <c r="E6" t="n">
-        <v>15.83244035045578</v>
+        <v>15.60928894368737</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.941382454972447</v>
+        <v>1.880827186567939</v>
       </c>
       <c r="C7" t="n">
-        <v>8.00011255813156</v>
+        <v>7.689767180818712</v>
       </c>
       <c r="D7" t="n">
-        <v>7.60107227614295</v>
+        <v>7.746612744136336</v>
       </c>
       <c r="E7" t="n">
-        <v>17.54256728924696</v>
+        <v>17.31720711152299</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.183408492417578</v>
+        <v>1.107085032696972</v>
       </c>
       <c r="C8" t="n">
-        <v>5.664670681736572</v>
+        <v>5.357261812172963</v>
       </c>
       <c r="D8" t="n">
-        <v>5.770186538507243</v>
+        <v>6.023153200899863</v>
       </c>
       <c r="E8" t="n">
-        <v>12.61826571266139</v>
+        <v>12.4875000457698</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.48501489036233</v>
+        <v>1.367274404443918</v>
       </c>
       <c r="C9" t="n">
-        <v>6.983348251052684</v>
+        <v>6.582695005955317</v>
       </c>
       <c r="D9" t="n">
-        <v>6.259608940166229</v>
+        <v>6.716274180724085</v>
       </c>
       <c r="E9" t="n">
-        <v>14.72797208158124</v>
+        <v>14.66624359112332</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.791511892872406</v>
+        <v>1.628047995983464</v>
       </c>
       <c r="C10" t="n">
-        <v>8.421062750215427</v>
+        <v>7.92101370111294</v>
       </c>
       <c r="D10" t="n">
-        <v>6.759447465402188</v>
+        <v>7.319120882708471</v>
       </c>
       <c r="E10" t="n">
-        <v>16.97202210849002</v>
+        <v>16.86818257980487</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.094407349564345</v>
+        <v>1.888197819087128</v>
       </c>
       <c r="C11" t="n">
-        <v>9.942720240954962</v>
+        <v>9.384400273996713</v>
       </c>
       <c r="D11" t="n">
-        <v>7.202018503247673</v>
+        <v>7.866462106804697</v>
       </c>
       <c r="E11" t="n">
-        <v>19.23914609376698</v>
+        <v>19.13906019988854</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.399306594144554</v>
+        <v>2.149182491465741</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49484622236273</v>
+        <v>10.89315577618797</v>
       </c>
       <c r="D12" t="n">
-        <v>7.613999869581683</v>
+        <v>8.459722886513395</v>
       </c>
       <c r="E12" t="n">
-        <v>21.50815268608897</v>
+        <v>21.50206115416711</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.699043950641857</v>
+        <v>2.397409109846025</v>
       </c>
       <c r="C13" t="n">
-        <v>13.08417768508789</v>
+        <v>12.5030508924184</v>
       </c>
       <c r="D13" t="n">
-        <v>8.066112269396642</v>
+        <v>9.012545617912155</v>
       </c>
       <c r="E13" t="n">
-        <v>23.84933390512639</v>
+        <v>23.91300562017658</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.557356200723758</v>
+        <v>1.391067774578433</v>
       </c>
       <c r="C14" t="n">
-        <v>9.152814211738928</v>
+        <v>8.805609318655002</v>
       </c>
       <c r="D14" t="n">
-        <v>6.081465606387995</v>
+        <v>6.812357137245659</v>
       </c>
       <c r="E14" t="n">
-        <v>16.79163601885068</v>
+        <v>17.0090342304791</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.597087530314626</v>
+        <v>1.400256933090183</v>
       </c>
       <c r="C15" t="n">
-        <v>9.757610067463133</v>
+        <v>9.519948583219067</v>
       </c>
       <c r="D15" t="n">
-        <v>6.06172266005559</v>
+        <v>6.878762551960913</v>
       </c>
       <c r="E15" t="n">
-        <v>17.41642025783335</v>
+        <v>17.79896806827016</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.861138392848849</v>
+        <v>1.607052269512731</v>
       </c>
       <c r="C16" t="n">
-        <v>11.44703096936217</v>
+        <v>11.2347967506581</v>
       </c>
       <c r="D16" t="n">
-        <v>6.478641457618084</v>
+        <v>7.410221854177883</v>
       </c>
       <c r="E16" t="n">
-        <v>19.78681081982911</v>
+        <v>20.25207087434871</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.50521558015121</v>
+        <v>1.278372955607942</v>
       </c>
       <c r="C17" t="n">
-        <v>10.43416186289074</v>
+        <v>10.33868689865274</v>
       </c>
       <c r="D17" t="n">
-        <v>5.974543463918475</v>
+        <v>6.914390176148031</v>
       </c>
       <c r="E17" t="n">
-        <v>17.91392090696042</v>
+        <v>18.53145003040871</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.728779167362294</v>
+        <v>1.44674268688627</v>
       </c>
       <c r="C18" t="n">
-        <v>12.14493577735714</v>
+        <v>12.06767223303292</v>
       </c>
       <c r="D18" t="n">
-        <v>6.34970853161935</v>
+        <v>7.422729319929986</v>
       </c>
       <c r="E18" t="n">
-        <v>20.22342347633879</v>
+        <v>20.93714423984918</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.744320233520521</v>
+        <v>1.442707703821815</v>
       </c>
       <c r="C19" t="n">
-        <v>12.9568509462463</v>
+        <v>12.89377365624844</v>
       </c>
       <c r="D19" t="n">
-        <v>6.42683463126498</v>
+        <v>7.541933126179634</v>
       </c>
       <c r="E19" t="n">
-        <v>21.1280058110318</v>
+        <v>21.87841448624989</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.960177101253267</v>
+        <v>1.592512586012836</v>
       </c>
       <c r="C20" t="n">
-        <v>14.85876132125252</v>
+        <v>14.85160438048856</v>
       </c>
       <c r="D20" t="n">
-        <v>6.793831558066524</v>
+        <v>8.088992399417085</v>
       </c>
       <c r="E20" t="n">
-        <v>23.61276998057231</v>
+        <v>24.53310936591848</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.17581959042232</v>
+        <v>0.9421636368115791</v>
       </c>
       <c r="C21" t="n">
-        <v>10.93585457471494</v>
+        <v>10.97006848220794</v>
       </c>
       <c r="D21" t="n">
-        <v>5.63052925087335</v>
+        <v>6.779331144474797</v>
       </c>
       <c r="E21" t="n">
-        <v>17.74220341601061</v>
+        <v>18.69156326349432</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250301289024606</v>
+        <v>1.253167992321007</v>
       </c>
       <c r="C3" t="n">
-        <v>4.638882475584779</v>
+        <v>4.664447185803367</v>
       </c>
       <c r="D3" t="n">
-        <v>6.181707049664754</v>
+        <v>6.09564704591048</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07089081427414</v>
+        <v>12.01326222403485</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.362317557640158</v>
+        <v>1.380960995755827</v>
       </c>
       <c r="C4" t="n">
-        <v>5.164271220097906</v>
+        <v>5.208972760706272</v>
       </c>
       <c r="D4" t="n">
-        <v>6.497396334888224</v>
+        <v>6.393273334162756</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02398511262629</v>
+        <v>12.98320709062486</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.513473540924739</v>
+        <v>1.548717671604346</v>
       </c>
       <c r="C5" t="n">
-        <v>5.83817498314566</v>
+        <v>5.923712796970821</v>
       </c>
       <c r="D5" t="n">
-        <v>6.867463977215419</v>
+        <v>6.662449608990448</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21911250128582</v>
+        <v>14.13488007756562</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.689271657366392</v>
+        <v>1.740840566609029</v>
       </c>
       <c r="C6" t="n">
-        <v>6.682171189649</v>
+        <v>6.802729536463533</v>
       </c>
       <c r="D6" t="n">
-        <v>7.237846096671976</v>
+        <v>6.97092795642599</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60928894368737</v>
+        <v>15.51449805949855</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.880827186567939</v>
+        <v>1.951915302600878</v>
       </c>
       <c r="C7" t="n">
-        <v>7.689767180818712</v>
+        <v>7.829587556748288</v>
       </c>
       <c r="D7" t="n">
-        <v>7.746612744136336</v>
+        <v>7.387243918586267</v>
       </c>
       <c r="E7" t="n">
-        <v>17.31720711152299</v>
+        <v>17.16874677793543</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.107085032696972</v>
+        <v>1.169234001760214</v>
       </c>
       <c r="C8" t="n">
-        <v>5.357261812172963</v>
+        <v>5.430159218218675</v>
       </c>
       <c r="D8" t="n">
-        <v>6.023153200899863</v>
+        <v>5.598578256174875</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4875000457698</v>
+        <v>12.19797147615376</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.367274404443918</v>
+        <v>1.44807395751784</v>
       </c>
       <c r="C9" t="n">
-        <v>6.582695005955317</v>
+        <v>6.655384239417427</v>
       </c>
       <c r="D9" t="n">
-        <v>6.716274180724085</v>
+        <v>6.100675479275449</v>
       </c>
       <c r="E9" t="n">
-        <v>14.66624359112332</v>
+        <v>14.20413367621072</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.628047995983464</v>
+        <v>1.739381193824144</v>
       </c>
       <c r="C10" t="n">
-        <v>7.92101370111294</v>
+        <v>7.993142185789081</v>
       </c>
       <c r="D10" t="n">
-        <v>7.319120882708471</v>
+        <v>6.569085449405438</v>
       </c>
       <c r="E10" t="n">
-        <v>16.86818257980487</v>
+        <v>16.30160882901866</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.888197819087128</v>
+        <v>2.047880717157745</v>
       </c>
       <c r="C11" t="n">
-        <v>9.384400273996713</v>
+        <v>9.419545791615379</v>
       </c>
       <c r="D11" t="n">
-        <v>7.866462106804697</v>
+        <v>7.081595721142416</v>
       </c>
       <c r="E11" t="n">
-        <v>19.13906019988854</v>
+        <v>18.54902222991554</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.149182491465741</v>
+        <v>2.36465700727214</v>
       </c>
       <c r="C12" t="n">
-        <v>10.89315577618797</v>
+        <v>10.91073097096369</v>
       </c>
       <c r="D12" t="n">
-        <v>8.459722886513395</v>
+        <v>7.579081065476538</v>
       </c>
       <c r="E12" t="n">
-        <v>21.50206115416711</v>
+        <v>20.85446904371237</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.397409109846025</v>
+        <v>2.671014503962278</v>
       </c>
       <c r="C13" t="n">
-        <v>12.5030508924184</v>
+        <v>12.41922511191333</v>
       </c>
       <c r="D13" t="n">
-        <v>9.012545617912155</v>
+        <v>7.996648023428494</v>
       </c>
       <c r="E13" t="n">
-        <v>23.91300562017658</v>
+        <v>23.0868876393041</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.391067774578433</v>
+        <v>1.551544254314617</v>
       </c>
       <c r="C14" t="n">
-        <v>8.805609318655002</v>
+        <v>8.747352409884996</v>
       </c>
       <c r="D14" t="n">
-        <v>6.812357137245659</v>
+        <v>6.07647832805042</v>
       </c>
       <c r="E14" t="n">
-        <v>17.0090342304791</v>
+        <v>16.37537499225003</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.400256933090183</v>
+        <v>1.589773509917987</v>
       </c>
       <c r="C15" t="n">
-        <v>9.519948583219067</v>
+        <v>9.312358031156077</v>
       </c>
       <c r="D15" t="n">
-        <v>6.878762551960913</v>
+        <v>6.091705234943289</v>
       </c>
       <c r="E15" t="n">
-        <v>17.79896806827016</v>
+        <v>16.99383677601735</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.607052269512731</v>
+        <v>1.848179323152791</v>
       </c>
       <c r="C16" t="n">
-        <v>11.2347967506581</v>
+        <v>10.95488084522325</v>
       </c>
       <c r="D16" t="n">
-        <v>7.410221854177883</v>
+        <v>6.552576877224912</v>
       </c>
       <c r="E16" t="n">
-        <v>20.25207087434871</v>
+        <v>19.35563704560095</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.278372955607942</v>
+        <v>1.482949542218892</v>
       </c>
       <c r="C17" t="n">
-        <v>10.33868689865274</v>
+        <v>10.0209540716503</v>
       </c>
       <c r="D17" t="n">
-        <v>6.914390176148031</v>
+        <v>6.080886375242488</v>
       </c>
       <c r="E17" t="n">
-        <v>18.53145003040871</v>
+        <v>17.58478998911168</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44674268688627</v>
+        <v>1.704677261223034</v>
       </c>
       <c r="C18" t="n">
-        <v>12.06767223303292</v>
+        <v>11.70393470860948</v>
       </c>
       <c r="D18" t="n">
-        <v>7.422729319929986</v>
+        <v>6.558428093542223</v>
       </c>
       <c r="E18" t="n">
-        <v>20.93714423984918</v>
+        <v>19.96704006337474</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.442707703821815</v>
+        <v>1.723458094805276</v>
       </c>
       <c r="C19" t="n">
-        <v>12.89377365624844</v>
+        <v>12.52308535807893</v>
       </c>
       <c r="D19" t="n">
-        <v>7.541933126179634</v>
+        <v>6.668864892792946</v>
       </c>
       <c r="E19" t="n">
-        <v>21.87841448624989</v>
+        <v>20.91540834567715</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.592512586012836</v>
+        <v>1.928790627148496</v>
       </c>
       <c r="C20" t="n">
-        <v>14.85160438048856</v>
+        <v>14.41184031384824</v>
       </c>
       <c r="D20" t="n">
-        <v>8.088992399417085</v>
+        <v>7.143294470870218</v>
       </c>
       <c r="E20" t="n">
-        <v>24.53310936591848</v>
+        <v>23.48392541186696</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9421636368115791</v>
+        <v>1.154594205056504</v>
       </c>
       <c r="C21" t="n">
-        <v>10.97006848220794</v>
+        <v>10.64887990328656</v>
       </c>
       <c r="D21" t="n">
-        <v>6.779331144474797</v>
+        <v>5.966758204623797</v>
       </c>
       <c r="E21" t="n">
-        <v>18.69156326349432</v>
+        <v>17.77023231296686</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_88_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253167992321007</v>
+        <v>2.598214456126799</v>
       </c>
       <c r="C3" t="n">
-        <v>4.664447185803367</v>
+        <v>7.694120824648481</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09564704591048</v>
+        <v>8.162120590963852</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01326222403485</v>
+        <v>18.45445587173913</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380960995755827</v>
+        <v>1.089548480750711</v>
       </c>
       <c r="C4" t="n">
-        <v>5.208972760706272</v>
+        <v>4.469922340800743</v>
       </c>
       <c r="D4" t="n">
-        <v>6.393273334162756</v>
+        <v>5.817140179735089</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98320709062486</v>
+        <v>11.37661100128654</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.548717671604346</v>
+        <v>1.197462441471497</v>
       </c>
       <c r="C5" t="n">
-        <v>5.923712796970821</v>
+        <v>5.085560574081361</v>
       </c>
       <c r="D5" t="n">
-        <v>6.662449608990448</v>
+        <v>6.151908340386896</v>
       </c>
       <c r="E5" t="n">
-        <v>14.13488007756562</v>
+        <v>12.43493135593975</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.740840566609029</v>
+        <v>1.315947675359247</v>
       </c>
       <c r="C6" t="n">
-        <v>6.802729536463533</v>
+        <v>5.84516380437765</v>
       </c>
       <c r="D6" t="n">
-        <v>6.97092795642599</v>
+        <v>6.540101039335071</v>
       </c>
       <c r="E6" t="n">
-        <v>15.51449805949855</v>
+        <v>13.70121251907197</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.951915302600878</v>
+        <v>1.440000506115841</v>
       </c>
       <c r="C7" t="n">
-        <v>7.829587556748288</v>
+        <v>6.791774875539642</v>
       </c>
       <c r="D7" t="n">
-        <v>7.387243918586267</v>
+        <v>6.90972376831558</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16874677793543</v>
+        <v>15.14149914997106</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.169234001760214</v>
+        <v>1.58542945638656</v>
       </c>
       <c r="C8" t="n">
-        <v>5.430159218218675</v>
+        <v>7.893394356648789</v>
       </c>
       <c r="D8" t="n">
-        <v>5.598578256174875</v>
+        <v>7.312043447214276</v>
       </c>
       <c r="E8" t="n">
-        <v>12.19797147615376</v>
+        <v>16.79086726024963</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.44807395751784</v>
+        <v>1.733032617377085</v>
       </c>
       <c r="C9" t="n">
-        <v>6.655384239417427</v>
+        <v>9.135627392732768</v>
       </c>
       <c r="D9" t="n">
-        <v>6.100675479275449</v>
+        <v>7.86012948637276</v>
       </c>
       <c r="E9" t="n">
-        <v>14.20413367621072</v>
+        <v>18.72878949648261</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.739381193824144</v>
+        <v>1.087079415435451</v>
       </c>
       <c r="C10" t="n">
-        <v>7.993142185789081</v>
+        <v>6.795186369898382</v>
       </c>
       <c r="D10" t="n">
-        <v>6.569085449405438</v>
+        <v>6.205558516204791</v>
       </c>
       <c r="E10" t="n">
-        <v>16.30160882901866</v>
+        <v>14.08782430153862</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.047880717157745</v>
+        <v>1.031060891431128</v>
       </c>
       <c r="C11" t="n">
-        <v>9.419545791615379</v>
+        <v>7.239918079922188</v>
       </c>
       <c r="D11" t="n">
-        <v>7.081595721142416</v>
+        <v>6.125241736520359</v>
       </c>
       <c r="E11" t="n">
-        <v>18.54902222991554</v>
+        <v>14.39622070787368</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.36465700727214</v>
+        <v>1.119604716877148</v>
       </c>
       <c r="C12" t="n">
-        <v>10.91073097096369</v>
+        <v>8.580445482685995</v>
       </c>
       <c r="D12" t="n">
-        <v>7.579081065476538</v>
+        <v>6.5528517665821</v>
       </c>
       <c r="E12" t="n">
-        <v>20.85446904371237</v>
+        <v>16.25290196614525</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.671014503962278</v>
+        <v>0.8868519711543138</v>
       </c>
       <c r="C13" t="n">
-        <v>12.41922511191333</v>
+        <v>8.19585563702435</v>
       </c>
       <c r="D13" t="n">
-        <v>7.996648023428494</v>
+        <v>6.032122966772549</v>
       </c>
       <c r="E13" t="n">
-        <v>23.0868876393041</v>
+        <v>15.11483057495121</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.551544254314617</v>
+        <v>0.9664029876294329</v>
       </c>
       <c r="C14" t="n">
-        <v>8.747352409884996</v>
+        <v>9.613950925900699</v>
       </c>
       <c r="D14" t="n">
-        <v>6.07647832805042</v>
+        <v>6.444761344344527</v>
       </c>
       <c r="E14" t="n">
-        <v>16.37537499225003</v>
+        <v>17.02511525787466</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.589773509917987</v>
+        <v>0.9418298425921352</v>
       </c>
       <c r="C15" t="n">
-        <v>9.312358031156077</v>
+        <v>10.38723432262774</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091705234943289</v>
+        <v>6.549209482599345</v>
       </c>
       <c r="E15" t="n">
-        <v>16.99383677601735</v>
+        <v>17.87827364781922</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.848179323152791</v>
+        <v>1.031178701155637</v>
       </c>
       <c r="C16" t="n">
-        <v>10.95488084522325</v>
+        <v>12.18727855584131</v>
       </c>
       <c r="D16" t="n">
-        <v>6.552576877224912</v>
+        <v>7.011887540656782</v>
       </c>
       <c r="E16" t="n">
-        <v>19.35563704560095</v>
+        <v>20.23034479765373</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.482949542218892</v>
+        <v>0.6187661255556373</v>
       </c>
       <c r="C17" t="n">
-        <v>10.0209540716503</v>
+        <v>9.203207321397919</v>
       </c>
       <c r="D17" t="n">
-        <v>6.080886375242488</v>
+        <v>5.863066012101249</v>
       </c>
       <c r="E17" t="n">
-        <v>17.58478998911168</v>
+        <v>15.6850394590548</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.704677261223034</v>
+        <v>0.4866621544721864</v>
       </c>
       <c r="C18" t="n">
-        <v>11.70393470860948</v>
+        <v>8.291301148831224</v>
       </c>
       <c r="D18" t="n">
-        <v>6.558428093542223</v>
+        <v>5.385151229673902</v>
       </c>
       <c r="E18" t="n">
-        <v>19.96704006337474</v>
+        <v>14.16311453297731</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.723458094805276</v>
+        <v>0.5711219094685396</v>
       </c>
       <c r="C19" t="n">
-        <v>12.52308535807893</v>
+        <v>10.30642666909119</v>
       </c>
       <c r="D19" t="n">
-        <v>6.668864892792946</v>
+        <v>5.976958563270921</v>
       </c>
       <c r="E19" t="n">
-        <v>20.91540834567715</v>
+        <v>16.85450714183065</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.928790627148496</v>
+        <v>0.6520179202984766</v>
       </c>
       <c r="C20" t="n">
-        <v>14.41184031384824</v>
+        <v>12.49363292695153</v>
       </c>
       <c r="D20" t="n">
-        <v>7.143294470870218</v>
+        <v>6.509527240393688</v>
       </c>
       <c r="E20" t="n">
-        <v>23.48392541186696</v>
+        <v>19.65517808764369</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.154594205056504</v>
+        <v>0.7231062715629882</v>
       </c>
       <c r="C21" t="n">
-        <v>10.64887990328656</v>
+        <v>14.67944510307184</v>
       </c>
       <c r="D21" t="n">
-        <v>5.966758204623797</v>
+        <v>6.999016828254105</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77023231296686</v>
+        <v>22.40156820288893</v>
       </c>
     </row>
   </sheetData>
